--- a/tolls.xlsx
+++ b/tolls.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="11520" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Project Stage</t>
   </si>
@@ -44,6 +44,18 @@
     <t>API_KEY_Model_Used</t>
   </si>
   <si>
+    <t>Preprocessing_Document_created</t>
+  </si>
+  <si>
+    <t>Chunking</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Email_Reading</t>
+  </si>
+  <si>
     <t>Stage1</t>
   </si>
   <si>
@@ -57,6 +69,84 @@
   </si>
   <si>
     <t>GROQ</t>
+  </si>
+  <si>
+    <t>RecursiveCharacterTextSplitter</t>
+  </si>
+  <si>
+    <t>Streanlit</t>
+  </si>
+  <si>
+    <t>IMAP (imaplib)</t>
+  </si>
+  <si>
+    <t>Stage2</t>
+  </si>
+  <si>
+    <t>Sentence_transformer=BAAI/bge-base-en-v1.6</t>
+  </si>
+  <si>
+    <t>llama-3.3-71b-versatile</t>
+  </si>
+  <si>
+    <t>Total documents created: 10069</t>
+  </si>
+  <si>
+    <t>Streamlit</t>
+  </si>
+  <si>
+    <t>Dimension = 768</t>
+  </si>
+  <si>
+    <t>chunk_size = 500
+chunk_overlap =  50                     Har chunk =500 characters
+Aur next chunk me 50 characters repeat honge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chunk 1 → characters 0–500
+Chunk 2 → characters 450–950
+Chunk 3 → characters 900–1400  50 characters repeat     </t>
+  </si>
+  <si>
+    <t>Why_embeding</t>
+  </si>
+  <si>
+    <t>Benefit</t>
+  </si>
+  <si>
+    <t>Customer Email
+   ↓
+Email Listener
+(read email)
+   ↓
+Query Embedding
+(email → vector)
+   ↓
+Vector Search
+(find relevant chunks)
+   ↓
+LLM
+(generate reply)
+   ↓
+AI Email Response</t>
+  </si>
+  <si>
+    <t>high quality embeddings</t>
+  </si>
+  <si>
+    <t>better semantic understanding</t>
+  </si>
+  <si>
+    <t>open source</t>
+  </si>
+  <si>
+    <t>free and fast</t>
+  </si>
+  <si>
+    <t>good for RAG</t>
+  </si>
+  <si>
+    <t>optimized for retrieval</t>
   </si>
 </sst>
 </file>
@@ -69,8 +159,16 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -532,153 +630,159 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -998,16 +1102,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="21.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="43.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="21.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="9.44444444444444" customWidth="1"/>
+    <col min="5" max="5" width="20.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="28.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1023,22 +1130,121 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="F2"/>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="72" spans="3:7">
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="57.6" spans="7:7">
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="216" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/tolls.xlsx
+++ b/tolls.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
     <t>llama-3.3-71b-versatile</t>
   </si>
   <si>
-    <t>Total documents created: 10069</t>
+    <t>Total documents created: 10082</t>
   </si>
   <si>
     <t>Streamlit</t>
@@ -159,7 +159,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,13 +169,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -630,148 +623,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1159,7 +1152,6 @@
       <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2"/>
       <c r="G2" t="s">
         <v>14</v>
       </c>
